--- a/files/九龙-何文田-太子道西233号.xlsx
+++ b/files/九龙-何文田-太子道西233号.xlsx
@@ -904,7 +904,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>2025-01-22</t>
+          <t>2025-01-23</t>
         </is>
       </c>
       <c r="H5" s="5" t="n">
@@ -970,7 +970,7 @@
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t>2025-05-01</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="H6" s="5" t="n">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H7" s="5" t="n">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t>2025-07-16</t>
+          <t>2025-07-17</t>
         </is>
       </c>
       <c r="H8" s="5" t="n">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="H9" s="5" t="n">
@@ -1234,7 +1234,7 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="H10" s="5" t="n">
@@ -1300,7 +1300,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>2025-02-20</t>
+          <t>2025-02-21</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H12" s="5" t="n">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H13" s="5" t="n">
@@ -1498,7 +1498,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2025-01-01</t>
+          <t>2025-01-02</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2024-12-29</t>
+          <t>2024-12-30</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2025-07-15</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2025-07-08</t>
+          <t>2025-07-09</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2024-12-26</t>
+          <t>2024-12-27</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2025-09-10</t>
+          <t>2025-09-11</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-02-04</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2224,7 +2224,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>2025-01-08</t>
+          <t>2025-01-09</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -2422,7 +2422,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-16</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -2488,7 +2488,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-02-15</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-12-19</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -2620,7 +2620,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>2024-12-22</t>
+          <t>2024-12-23</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2686,7 +2686,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-03</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2752,7 +2752,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2025-10-09</t>
+          <t>2025-10-10</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2818,7 +2818,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2950,7 +2950,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2025-02-16</t>
+          <t>2025-02-17</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2025-06-29</t>
+          <t>2025-06-30</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3082,7 +3082,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3214,7 +3214,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2025-03-04</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2025-09-25</t>
+          <t>2025-09-26</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3482,7 +3482,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3548,7 +3548,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2025-02-19</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2025-09-28</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2024-11-27</t>
+          <t>2024-11-28</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4282,7 +4282,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2024-12-27</t>
+          <t>2024-12-28</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2025-08-12</t>
+          <t>2025-08-13</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4414,7 +4414,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4480,7 +4480,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2025-11-23</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4612,7 +4612,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2025-07-27</t>
+          <t>2025-07-28</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4678,7 +4678,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2025-07-15</t>
+          <t>2025-07-16</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4744,7 +4744,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4876,7 +4876,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -4942,7 +4942,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5008,7 +5008,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2025-07-28</t>
+          <t>2025-07-29</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2025-08-27</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5140,7 +5140,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5206,7 +5206,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2025-08-21</t>
+          <t>2025-08-22</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5338,7 +5338,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2025-06-01</t>
+          <t>2025-06-02</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2025-08-26</t>
+          <t>2025-08-27</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2025-07-07</t>
+          <t>2025-07-08</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2025-05-22</t>
+          <t>2025-05-23</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5602,7 +5602,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2025-05-21</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5668,7 +5668,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2025-06-09</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5883,7 +5883,7 @@
           <t>A | 1748呎 (4+房)
 $7338万
 $41,979/呎
-(25年-05月-01日)</t>
+(25年-05月-02日)</t>
         </is>
       </c>
       <c r="C6" s="22" t="inlineStr">
@@ -5891,7 +5891,7 @@
           <t>B | 1530呎 (4+房)
 $6378万
 $41,686/呎
-(25年-01月-22日)</t>
+(25年-01月-23日)</t>
         </is>
       </c>
       <c r="D6" s="21" t="inlineStr"/>
@@ -5911,7 +5911,7 @@
           <t>A | 1039呎 (4+房)
 $3117万
 $30,000/呎
-(25年-02月-20日)</t>
+(25年-02月-21日)</t>
         </is>
       </c>
       <c r="C7" s="22" t="inlineStr">
@@ -5919,7 +5919,7 @@
           <t>B | 1039呎 (4+房)
 $3138万
 $30,202/呎
-(25年-03月-25日)</t>
+(25年-03月-26日)</t>
         </is>
       </c>
       <c r="D7" s="22" t="inlineStr">
@@ -5927,7 +5927,7 @@
           <t>C | 966呎 (4+房)
 $2460万
 $25,466/呎
-(25年-11月-19日)</t>
+(25年-11月-20日)</t>
         </is>
       </c>
       <c r="E7" s="22" t="inlineStr">
@@ -5935,7 +5935,7 @@
           <t>D | 505呎 (2房)
 $1240万
 $24,554/呎
-(25年-07月-16日)</t>
+(25年-07月-17日)</t>
         </is>
       </c>
       <c r="F7" s="22" t="inlineStr">
@@ -5943,7 +5943,7 @@
           <t>E | 971呎 (4+房)
 $2750万
 $28,321/呎
-(25年-12月-10日)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr"/>
@@ -5960,7 +5960,7 @@
           <t>A | 1039呎 (4+房)
 $2980万
 $28,681/呎
-(24年-12月-29日)</t>
+(24年-12月-30日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -5968,7 +5968,7 @@
           <t>B | 1039呎 (4+房)
 $3014万
 $29,010/呎
-(25年-01月-01日)</t>
+(25年-01月-02日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -5976,7 +5976,7 @@
           <t>C | 966呎 (4+房)
 $2630万
 $27,226/呎
-(25年-11月-02日)</t>
+(25年-11月-03日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -5984,7 +5984,7 @@
           <t>D | 505呎 (2房)
 $1225万
 $24,257/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -5992,7 +5992,7 @@
           <t>E | 971呎 (4+房)
 $2631万
 $27,096/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="G8" s="21" t="inlineStr"/>
@@ -6009,7 +6009,7 @@
           <t>A | 1039呎 (4+房)
 $2947万
 $28,363/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -6017,7 +6017,7 @@
           <t>B | 1039呎 (4+房)
 $2650万
 $25,505/呎
-(24年-12月-26日)</t>
+(24年-12月-27日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -6025,7 +6025,7 @@
           <t>C | 966呎 (4+房)
 $2283万
 $23,634/呎
-(25年-05月-07日)</t>
+(25年-05月-08日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -6033,7 +6033,7 @@
           <t>D | 505呎 (2房)
 $1215万
 $24,059/呎
-(25年-07月-08日)</t>
+(25年-07月-09日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -6041,7 +6041,7 @@
           <t>E | 971呎 (4+房)
 $2588万
 $26,653/呎
-(25年-07月-14日)</t>
+(25年-07月-15日)</t>
         </is>
       </c>
       <c r="G9" s="21" t="inlineStr"/>
@@ -6058,7 +6058,7 @@
           <t>A | 1039呎 (4+房)
 $2920万
 $28,104/呎
-(25年-01月-08日)</t>
+(25年-01月-09日)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -6066,7 +6066,7 @@
           <t>B | 1039呎 (4+房)
 $2863万
 $27,555/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">
@@ -6074,7 +6074,7 @@
           <t>C | 966呎 (4+房)
 $2570万
 $26,605/呎
-(26年-02月-04日)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6082,7 +6082,7 @@
           <t>D | 505呎 (2房)
 $1205万
 $23,861/呎
-(25年-09月-10日)</t>
+(25年-09月-11日)</t>
         </is>
       </c>
       <c r="F10" s="22" t="inlineStr">
@@ -6090,7 +6090,7 @@
           <t>E | 971呎 (4+房)
 $2580万
 $26,571/呎
-(26年-01月-19日)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="G10" s="21" t="inlineStr"/>
@@ -6107,7 +6107,7 @@
           <t>A | 1039呎 (4+房)
 $2849万
 $27,419/呎
-(24年-12月-22日)</t>
+(24年-12月-23日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -6115,7 +6115,7 @@
           <t>B | 1039呎 (4+房)
 $2860万
 $27,526/呎
-(24年-12月-18日)</t>
+(24年-12月-19日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -6123,7 +6123,7 @@
           <t>C | 966呎 (4+房)
 $2271万
 $23,509/呎
-(26年-02月-15日)</t>
+(26年-02月-16日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -6131,7 +6131,7 @@
           <t>D | 505呎 (2房)
 $1198万
 $23,723/呎
-(25年-09月-15日)</t>
+(25年-09月-16日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -6139,7 +6139,7 @@
           <t>E | 971呎 (4+房)
 $2268万
 $23,357/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="G11" s="21" t="inlineStr"/>
@@ -6156,7 +6156,7 @@
           <t>A | 1039呎 (4+房)
 $2509万
 $24,146/呎
-(25年-02月-16日)</t>
+(25年-02月-17日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -6164,7 +6164,7 @@
           <t>B | 1039呎 (4+房)
 $2829万
 $27,226/呎
-(25年-02月-26日)</t>
+(25年-02月-27日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -6172,7 +6172,7 @@
           <t>C | 966呎 (4+房)
 $2465万
 $25,518/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -6180,7 +6180,7 @@
           <t>D | 505呎 (2房)
 $1183万
 $23,426/呎
-(25年-10月-09日)</t>
+(25年-10月-10日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -6188,7 +6188,7 @@
           <t>E | 971呎 (4+房)
 $2275万
 $23,429/呎
-(26年-02月-02日)</t>
+(26年-02月-03日)</t>
         </is>
       </c>
       <c r="G12" s="21" t="inlineStr"/>
@@ -6205,7 +6205,7 @@
           <t>A | 1039呎 (4+房)
 $2868万
 $27,603/呎
-(25年-09月-08日)</t>
+(25年-09月-09日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -6213,7 +6213,7 @@
           <t>B | 1039呎 (4+房)
 $2850万
 $27,430/呎
-(25年-03月-04日)</t>
+(25年-03月-05日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -6221,7 +6221,7 @@
           <t>C | 966呎 (4+房)
 $2582万
 $26,729/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -6229,7 +6229,7 @@
           <t>D | 505呎 (2房)
 $1175万
 $23,267/呎
-(25年-12月-11日)</t>
+(25年-12月-12日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -6237,7 +6237,7 @@
           <t>E | 971呎 (4+房)
 $2250万
 $23,172/呎
-(25年-06月-29日)</t>
+(25年-06月-30日)</t>
         </is>
       </c>
       <c r="G13" s="21" t="inlineStr"/>
@@ -6254,7 +6254,7 @@
           <t>A | 1039呎 (4+房)
 $2500万
 $24,062/呎
-(25年-09月-17日)</t>
+(25年-09月-18日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -6262,7 +6262,7 @@
           <t>B | 1039呎 (4+房)
 $2800万
 $26,949/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -6270,7 +6270,7 @@
           <t>C | 842呎 (3房)
 $1866万
 $22,162/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -6278,7 +6278,7 @@
           <t>D | 668呎 (3房)
 $1440万
 $21,557/呎
-(25年-09月-25日)</t>
+(25年-09月-26日)</t>
         </is>
       </c>
       <c r="F14" s="20" t="inlineStr">
@@ -6303,7 +6303,7 @@
           <t>A | 1039呎 (4+房)
 $2650万
 $25,505/呎
-(25年-02月-19日)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -6311,7 +6311,7 @@
           <t>B | 1039呎 (4+房)
 $2410万
 $23,195/呎
-(25年-12月-04日)</t>
+(25年-12月-05日)</t>
         </is>
       </c>
       <c r="D15" s="20" t="inlineStr">
@@ -6327,7 +6327,7 @@
           <t>D | 668呎 (3房)
 $1410万
 $21,108/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -6335,7 +6335,7 @@
           <t>E | 884呎 (3房)
 $1920万
 $21,719/呎
-(26年-02月-11日)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="G15" s="21" t="inlineStr"/>
@@ -6352,7 +6352,7 @@
           <t>A | 1039呎 (4+房)
 $2435万
 $23,436/呎
-(24年-12月-27日)</t>
+(24年-12月-28日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -6360,7 +6360,7 @@
           <t>B | 1039呎 (4+房)
 $2405万
 $23,147/呎
-(24年-11月-27日)</t>
+(24年-11月-28日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -6368,7 +6368,7 @@
           <t>C | 842呎 (3房)
 $1806万
 $21,449/呎
-(25年-09月-28日)</t>
+(25年-09月-29日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -6376,7 +6376,7 @@
           <t>D | 668呎 (3房)
 $1435万
 $21,482/呎
-(25年-09月-29日)</t>
+(25年-09月-30日)</t>
         </is>
       </c>
       <c r="F16" s="20" t="inlineStr">
@@ -6401,7 +6401,7 @@
           <t>A | 492呎 (2房)
 $1107万
 $22,500/呎
-(25年-11月-20日)</t>
+(25年-11月-21日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -6409,7 +6409,7 @@
           <t>B | 376呎 (2房)
 $815万
 $21,676/呎
-(25年-07月-15日)</t>
+(25年-07月-16日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -6417,7 +6417,7 @@
           <t>C | 375呎 (2房)
 $802万
 $21,387/呎
-(25年-07月-27日)</t>
+(25年-07月-28日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -6425,7 +6425,7 @@
           <t>D | 495呎 (2房)
 $1114万
 $22,500/呎
-(25年-11月-23日)</t>
+(25年-11月-24日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -6433,7 +6433,7 @@
           <t>E | 844呎 (3房)
 $1755万
 $20,794/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -6441,7 +6441,7 @@
           <t>F | 668呎 (3房)
 $1408万
 $21,078/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="H17" s="22" t="inlineStr">
@@ -6449,7 +6449,7 @@
           <t>G | 884呎 (3房)
 $1822万
 $20,614/呎
-(25年-08月-12日)</t>
+(25年-08月-13日)</t>
         </is>
       </c>
     </row>
@@ -6464,7 +6464,7 @@
           <t>A | 492呎 (2房)
 $1059万
 $21,520/呎
-(25年-08月-21日)</t>
+(25年-08月-22日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -6472,7 +6472,7 @@
           <t>B | 376呎 (2房)
 $809万
 $21,516/呎
-(25年-06月-15日)</t>
+(25年-06月-16日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -6480,7 +6480,7 @@
           <t>C | 375呎 (2房)
 $801万
 $21,360/呎
-(25年-08月-27日)</t>
+(25年-08月-28日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -6488,7 +6488,7 @@
           <t>D | 495呎 (2房)
 $1061万
 $21,434/呎
-(25年-07月-28日)</t>
+(25年-07月-29日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -6496,7 +6496,7 @@
           <t>E | 844呎 (3房)
 $1750万
 $20,735/呎
-(25年-11月-06日)</t>
+(25年-11月-07日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -6504,7 +6504,7 @@
           <t>F | 668呎 (3房)
 $1420万
 $21,257/呎
-(25年-09月-22日)</t>
+(25年-09月-23日)</t>
         </is>
       </c>
       <c r="H18" s="22" t="inlineStr">
@@ -6512,7 +6512,7 @@
           <t>G | 884呎 (3房)
 $1818万
 $20,566/呎
-(25年-11月-10日)</t>
+(25年-11月-11日)</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
           <t>A | 469呎 (2房)
 $1027万
 $21,900/呎
-(25年-06月-09日)</t>
+(25年-06月-10日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -6535,7 +6535,7 @@
           <t>B | 376呎 (2房)
 $806万
 $21,436/呎
-(25年-05月-21日)</t>
+(25年-05月-22日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -6543,7 +6543,7 @@
           <t>C | 375呎 (2房)
 $810万
 $21,600/呎
-(25年-05月-22日)</t>
+(25年-05月-23日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -6551,7 +6551,7 @@
           <t>D | 473呎 (2房)
 $1025万
 $21,671/呎
-(25年-07月-07日)</t>
+(25年-07月-08日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -6559,7 +6559,7 @@
           <t>E | 809呎 (3房)
 $1783万
 $22,040/呎
-(25年-08月-26日)</t>
+(25年-08月-27日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -6567,7 +6567,7 @@
           <t>F | 636呎 (3房)
 $1396万
 $21,954/呎
-(25年-06月-01日)</t>
+(25年-06月-02日)</t>
         </is>
       </c>
       <c r="H19" s="22" t="inlineStr">
@@ -6575,7 +6575,7 @@
           <t>G | 849呎 (3房)
 $2290万
 $26,973/呎
-(26年-06月-01日)</t>
+(26年-06月-02日)</t>
         </is>
       </c>
     </row>
